--- a/winners.xlsx
+++ b/winners.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
     <t>Ticket Number</t>
   </si>
@@ -22,16 +22,10 @@
     <t>Prize</t>
   </si>
   <si>
-    <t>Electric Jug (Yasuda)</t>
+    <t>Yasuda Oven</t>
   </si>
   <si>
-    <t>Iron (Yasuda)</t>
-  </si>
-  <si>
-    <t>Washing Machine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Electric Jug </t>
+    <t>Pulsar</t>
   </si>
 </sst>
 </file>
@@ -389,7 +383,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
+  <dimension ref="A1:B3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -402,7 +396,7 @@
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>16938</v>
+        <v>20628</v>
       </c>
       <c r="B2" t="s">
         <v>2</v>
@@ -410,42 +404,10 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>14245</v>
+        <v>14649</v>
       </c>
       <c r="B3" t="s">
         <v>3</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>19050</v>
-      </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>22590</v>
-      </c>
-      <c r="B5" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>12108</v>
-      </c>
-      <c r="B6" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>19160</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
